--- a/artfynd/A 25448-2024 artfynd.xlsx
+++ b/artfynd/A 25448-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>100563090</v>
+        <v>79153519</v>
       </c>
       <c r="B2" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -708,24 +703,40 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tybyn, Dlr</t>
+          <t>5m N om rågång, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>457498.8871604733</v>
+        <v>457268</v>
       </c>
       <c r="R2" t="n">
-        <v>6669677.912121539</v>
+        <v>6669787</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,22 +760,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-05-06</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-07-17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-05-06</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-07-17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,77 +781,64 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Anders Erixon</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Anders Erixon</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>110376565</v>
+        <v>100563090</v>
       </c>
       <c r="B3" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tybyn, Tyfors, Dlr</t>
+          <t>Tybyn, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>457407.7389560592</v>
+        <v>457499</v>
       </c>
       <c r="R3" t="n">
-        <v>6669858.680342702</v>
+        <v>6669678</v>
       </c>
       <c r="S3" t="n">
-        <v>150</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,22 +862,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>08:30</t>
+          <t>2022-05-06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>08:30</t>
+          <t>2022-05-06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,18 +876,19 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Johan Thyberg</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Johan Thyberg</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
